--- a/data/output/evaluasi_65.xlsx
+++ b/data/output/evaluasi_65.xlsx
@@ -9,6 +9,10 @@
   <sheets>
     <sheet name="6500" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="6503" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="6502" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="6504" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="6571" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6501" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +480,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.24195142338084</v>
+        <v>5.241951423381137</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -485,7 +489,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -500,20 +504,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.212946224525549</v>
+        <v>-43.84371529291969</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pkp_q2-25</t>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -528,20 +532,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1560053306684852</v>
+        <v>4.619829551527008</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pkrt_q1-25 vs q-to-q_pkrt_q1-25.1</t>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
         </is>
       </c>
     </row>
@@ -556,20 +560,524 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.575217444872926</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0.9035276122723522</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="D6" t="n">
+        <v>-8.671866296570505</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.712582449693731</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>65</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.059176157651963</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.247150894305777</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>65</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8.575217444872926</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>65</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.797010242719336</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>65</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.26949747057835</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>65</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.271564077806002</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25 vs c-to-c_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>65</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-6.666184027509598</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>65</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.37363229757097</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>65</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.846658427108841</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25 vs implisit_q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>65</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.268692227657524</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>65</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2372715620805767</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25 vs implisit_q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>65</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9897912569406753</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>65</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2.014989943274256</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>65</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.686653065097054</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>65</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3.638169044736027</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>65</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kalimantan Utara</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.430408171201364</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25 vs implisit_y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -584,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,20 +1138,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0133490240049365</v>
+        <v>-0.01364023535663365</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -662,16 +1170,872 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0001750408618598534</v>
+        <v>-0.3757230745460005</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>implisit_y-on-y_pdrb_q1-25_ril vs implisit_y-on-y_pdrb_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.001214757297360705</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_q_pkp_q2-25_ril vs sog_q_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5661268821568725</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_q_net_ekspor_q2-25_ril vs sog_q_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-6.209627656658383</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>21.29142106702766</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5132758126512729</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-18.14776410947156</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-12.95152798440989</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.2249874438940988</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.706409963612559</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.747104225859087</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.093395435884496</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.510466375238265</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25_ril vs y-on-y_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.093395435884496</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.04375117944421</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.0899834085054849</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1543472431785011</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.687534399781623</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Nunukan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.02643254035961231</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25_ril vs implisit_q-to-q_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Nunukan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.749257873010624</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Nunukan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.06166578980345908</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.62352662372901</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.967589442587701</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3424815808520763</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6501</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Malinau</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.095587742700897</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_65.xlsx
+++ b/data/output/evaluasi_65.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
